--- a/data/football/exports/reporting/top_plays_report.xlsx
+++ b/data/football/exports/reporting/top_plays_report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:43:06</t>
+          <t>2026-05-26 14:31:40</t>
         </is>
       </c>
     </row>

--- a/data/football/exports/reporting/top_plays_report.xlsx
+++ b/data/football/exports/reporting/top_plays_report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:31:40</t>
+          <t>2026-05-27 15:07:10</t>
         </is>
       </c>
     </row>

--- a/data/football/exports/reporting/top_plays_report.xlsx
+++ b/data/football/exports/reporting/top_plays_report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-27 15:07:10</t>
+          <t>2026-05-28 09:02:51</t>
         </is>
       </c>
     </row>

--- a/data/football/exports/reporting/top_plays_report.xlsx
+++ b/data/football/exports/reporting/top_plays_report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-28 09:02:51</t>
+          <t>2026-05-28 17:31:14</t>
         </is>
       </c>
     </row>

--- a/data/football/exports/reporting/top_plays_report.xlsx
+++ b/data/football/exports/reporting/top_plays_report.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:31:14</t>
+          <t>2026-05-28 19:58:22</t>
         </is>
       </c>
     </row>
